--- a/机器人点位映射关系.xlsx
+++ b/机器人点位映射关系.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Robotic\RoboticManipulation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F70A601-68B9-472A-813E-186E054A8088}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44C16808-BD0A-4D33-895F-CA51CC07D197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{CDDD5614-B249-45A2-B234-AC811943B192}"/>
   </bookViews>
@@ -46,10 +46,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>5.8,6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>6.5, 6.7</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -114,14 +110,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>5.7, -5.8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6.4, -6.6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>7.3, -7.5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -151,6 +139,18 @@
   </si>
   <si>
     <t>(7.8,0.1）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.5, -6.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5.8, -5.8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5.8, 5.8</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -599,37 +599,37 @@
     </row>
     <row r="2" spans="1:20" ht="31.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="P2" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q2" t="s">
         <v>5</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>6</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>7</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>8</v>
-      </c>
-      <c r="T2" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="31.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -644,7 +644,7 @@
     </row>
     <row r="5" spans="1:20" ht="31.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K5">
         <v>3</v>
@@ -652,13 +652,13 @@
     </row>
     <row r="6" spans="1:20" ht="31.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="P6" t="s">
         <v>0</v>
@@ -666,10 +666,10 @@
     </row>
     <row r="7" spans="1:20" ht="31.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="E7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Q7" t="s">
         <v>1</v>
@@ -677,41 +677,41 @@
     </row>
     <row r="8" spans="1:20" ht="31.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="D8" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="K8" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="O8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R8" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="31.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="C9" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="K9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="S9" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="31.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K10" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="P10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T10" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="31.25" customHeight="1" x14ac:dyDescent="0.4">
